--- a/output/2026-09-01_11_Italia_Liguria_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-01_11_Italia_Liguria_Utensilerie_e_Macchine_Utensili.xlsx
@@ -1096,7 +1096,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Riscontro parziale: elencata come rivenditore/punto vendita in una rete di distribuzione utensili (elenco dealer Fasanotools). Informazioni pubbliche limitate.</t>
+          <t>Riscontro parziale: elencata come rivenditore/punto vendita in una rete di distribuzione utensili (elenco dealer Fasanotools). Informazioni pubbliche limitate. [DUPLICATO — vedi anche: 2026-09-01_10_Italia_Liguria_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
